--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -597,58 +597,58 @@
         <v>95</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.03157894736842105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.03241491085899514</v>
+        <v>0.03079416531604538</v>
       </c>
     </row>
   </sheetData>
@@ -1088,82 +1088,82 @@
         <v>95</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.03157894736842105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
@@ -1193,49 +1193,49 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -1265,19 +1265,19 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -1289,19 +1289,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1385,19 +1385,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0226904376012966</v>
+        <v>0.02593192868719611</v>
       </c>
     </row>
   </sheetData>
@@ -1603,10 +1603,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="4">
@@ -1636,12 +1636,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -1660,156 +1660,156 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.025</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -1819,21 +1819,21 @@
         <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1843,21 +1843,21 @@
         <v>26</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03846153846153846</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
@@ -1876,43 +1876,43 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Eletiva</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1948,12 +1948,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Eletiva</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -1972,12 +1972,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Finanças</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1996,12 +1996,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Finanças</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
@@ -2020,19 +2020,19 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04849498327759198</v>
+        <v>0.05183946488294314</v>
       </c>
     </row>
   </sheetData>
@@ -2214,34 +2214,34 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="5">
@@ -2271,84 +2271,84 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -2367,156 +2367,156 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.025</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03846153846153846</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.03846153846153846</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03846153846153846</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Eletiva</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -2535,12 +2535,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Eletiva</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -2559,12 +2559,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Finanças</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -2583,19 +2583,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Finanças</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -2607,19 +2607,19 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -2631,19 +2631,19 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Projeto</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -2655,19 +2655,19 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0</v>
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04013377926421405</v>
       </c>
     </row>
   </sheetData>
@@ -2834,49 +2834,49 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.103448275862069</v>
+        <v>0.03896103896103896</v>
       </c>
     </row>
     <row r="6">
@@ -2906,7 +2906,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2915,112 +2915,112 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03174603174603174</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.0425531914893617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.06896551724137931</v>
       </c>
     </row>
     <row r="12">
@@ -3098,12 +3098,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -3113,21 +3113,21 @@
         <v>30</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03823178016726404</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
   </sheetData>
@@ -3373,49 +3373,49 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.05</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.03174603174603174</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="5">
@@ -3517,25 +3517,25 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3661,67 +3661,67 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3733,19 +3733,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3757,19 +3757,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3936,25 +3936,25 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.04411764705882353</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
     <row r="4">
@@ -4032,73 +4032,73 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="10">
@@ -4200,25 +4200,25 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="15">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0352112676056338</v>
+        <v>0.03661971830985915</v>
       </c>
     </row>
   </sheetData>
@@ -4514,106 +4514,106 @@
         <v>68</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07352941176470588</v>
+        <v>0.05882352941176471</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.05</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="9">
@@ -4667,84 +4667,84 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.025</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03846153846153846</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
@@ -4754,28 +4754,28 @@
         <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4787,19 +4787,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4811,19 +4811,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -597,58 +597,58 @@
         <v>95</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.03157894736842105</v>
+        <v>0.04210526315789474</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
@@ -678,12 +678,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -702,12 +702,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -717,10 +717,10 @@
         <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03125</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="10">
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.03079416531604538</v>
+        <v>0.03241491085899514</v>
       </c>
     </row>
   </sheetData>
@@ -1088,82 +1088,82 @@
         <v>95</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.03157894736842105</v>
+        <v>0.04210526315789474</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0375</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
@@ -1193,49 +1193,49 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1289,19 +1289,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1385,19 +1385,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02593192868719611</v>
+        <v>0.02431118314424635</v>
       </c>
     </row>
   </sheetData>
@@ -2810,103 +2810,103 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.03896103896103896</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.103448275862069</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04838709677419355</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2930,132 +2930,132 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.06451612903225806</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -3065,45 +3065,45 @@
         <v>32</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.02127659574468085</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -3122,67 +3122,67 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.007936507936507936</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3218,19 +3218,19 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Projeto</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -3242,19 +3242,19 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.03464755077658303</v>
       </c>
     </row>
   </sheetData>
@@ -3397,73 +3397,73 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.02597402597402598</v>
       </c>
     </row>
     <row r="7">
@@ -3517,25 +3517,25 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -3546,31 +3546,31 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -3589,84 +3589,84 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.01298701298701299</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -3685,43 +3685,43 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>0.007936507936507936</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3733,19 +3733,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3757,19 +3757,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3781,19 +3781,19 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.02986857825567503</v>
+        <v>0.03225806451612903</v>
       </c>
     </row>
   </sheetData>
@@ -3936,121 +3936,121 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.04411764705882353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.05</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
@@ -4080,36 +4080,36 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -4128,60 +4128,60 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.01851851851851852</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -4191,45 +4191,45 @@
         <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -4296,19 +4296,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03661971830985915</v>
+        <v>0.03943661971830986</v>
       </c>
     </row>
   </sheetData>
@@ -4523,7 +4523,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4532,37 +4532,37 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>0.07142857142857142</v>
@@ -4571,12 +4571,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -4595,108 +4595,108 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.025</v>
+        <v>0.01851851851851852</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -4715,25 +4715,25 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="14">
@@ -4787,19 +4787,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4816,14 +4816,14 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -4835,19 +4835,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -4883,12 +4883,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -573,10 +573,10 @@
         <v>80</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.075</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="4">
@@ -606,49 +606,49 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
@@ -1097,121 +1097,121 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.05</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="9">
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02431118314424635</v>
+        <v>0.02593192868719611</v>
       </c>
     </row>
   </sheetData>
@@ -1603,10 +1603,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="4">
@@ -1660,60 +1660,60 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.05</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -1732,12 +1732,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -1756,60 +1756,60 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -1819,76 +1819,76 @@
         <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.05183946488294314</v>
+        <v>0.04682274247491638</v>
       </c>
     </row>
   </sheetData>
@@ -2214,10 +2214,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="4">
@@ -2247,12 +2247,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2271,49 +2271,49 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="8">
@@ -2324,31 +2324,31 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -2367,12 +2367,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -2415,91 +2415,91 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03846153846153846</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04013377926421405</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
   </sheetData>
@@ -2882,121 +2882,121 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04838709677419355</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="11">
@@ -3007,68 +3007,68 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03125</v>
+        <v>0.06451612903225806</v>
       </c>
     </row>
     <row r="14">
@@ -3122,67 +3122,67 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.007936507936507936</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3194,19 +3194,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3242,12 +3242,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03464755077658303</v>
+        <v>0.03584229390681003</v>
       </c>
     </row>
   </sheetData>
@@ -3421,180 +3421,180 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.02597402597402598</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.02597402597402598</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -3613,36 +3613,36 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
@@ -3661,12 +3661,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -3685,25 +3685,25 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.007936507936507936</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -3781,19 +3781,19 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.03106332138590203</v>
       </c>
     </row>
   </sheetData>
@@ -3936,121 +3936,121 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.04411764705882353</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="8">
@@ -4080,36 +4080,36 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -4128,36 +4128,36 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -4167,82 +4167,82 @@
         <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.025</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.01785714285714286</v>
       </c>
     </row>
     <row r="16">
@@ -4296,19 +4296,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03943661971830986</v>
+        <v>0.0352112676056338</v>
       </c>
     </row>
   </sheetData>
@@ -4499,55 +4499,55 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04411764705882353</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -4556,16 +4556,16 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="7">
@@ -4643,60 +4643,60 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -4715,36 +4715,36 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
@@ -4754,28 +4754,28 @@
         <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4787,19 +4787,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4811,12 +4811,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -4835,19 +4835,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4859,12 +4859,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -4883,19 +4883,19 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03661971830985915</v>
+        <v>0.03943661971830986</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2247,12 +2247,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2271,49 +2271,49 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="8">
@@ -2324,31 +2324,31 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -2367,12 +2367,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -2391,25 +2391,25 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="12">
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.0451505016722408</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -573,10 +573,10 @@
         <v>80</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="4">
@@ -606,49 +606,49 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
@@ -678,12 +678,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -702,12 +702,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -717,34 +717,34 @@
         <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="11">
@@ -755,14 +755,14 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -798,19 +798,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -822,19 +822,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -846,19 +846,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -870,19 +870,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -894,19 +894,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -918,19 +918,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1097,121 +1097,121 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0375</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02593192868719611</v>
+        <v>0.0226904376012966</v>
       </c>
     </row>
   </sheetData>
@@ -1627,10 +1627,10 @@
         <v>54</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.09259259259259259</v>
+        <v>0.07407407407407407</v>
       </c>
     </row>
     <row r="5">
@@ -1660,49 +1660,49 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="8">
@@ -1713,92 +1713,92 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="12">
@@ -2247,7 +2247,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2271,49 +2271,49 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="8">
@@ -2324,31 +2324,31 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -2367,12 +2367,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -2391,25 +2391,25 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="12">
@@ -2439,12 +2439,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0451505016722408</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
   </sheetData>
@@ -3951,10 +3951,10 @@
         <v>108</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.04629629629629629</v>
       </c>
     </row>
     <row r="4">
@@ -3984,84 +3984,84 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.05</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -4080,36 +4080,36 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.01785714285714286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -4119,130 +4119,130 @@
         <v>28</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.01785714285714286</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="16">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0352112676056338</v>
+        <v>0.0323943661971831</v>
       </c>
     </row>
   </sheetData>
@@ -4514,10 +4514,10 @@
         <v>108</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="5">
@@ -4547,25 +4547,25 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
@@ -4643,49 +4643,49 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.01785714285714286</v>
       </c>
     </row>
     <row r="12">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03943661971830986</v>
+        <v>0.04225352112676056</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -678,12 +678,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -702,12 +702,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -717,34 +717,34 @@
         <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03125</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.02222222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -755,14 +755,14 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -798,19 +798,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -822,19 +822,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -846,19 +846,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -870,19 +870,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -894,19 +894,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -918,19 +918,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1112,10 +1112,10 @@
         <v>80</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5">
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0226904376012966</v>
+        <v>0.02431118314424635</v>
       </c>
     </row>
   </sheetData>
@@ -1627,10 +1627,10 @@
         <v>54</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07407407407407407</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="5">
@@ -1651,82 +1651,82 @@
         <v>28</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1153846153846154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="9">
@@ -1804,12 +1804,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -1828,25 +1828,25 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="14">
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04682274247491638</v>
+        <v>0.05351170568561873</v>
       </c>
     </row>
   </sheetData>
@@ -2415,36 +2415,36 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.025</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -2463,43 +2463,43 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04180602006688963</v>
       </c>
     </row>
   </sheetData>
@@ -2825,58 +2825,58 @@
         <v>63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07936507936507936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.06451612903225806</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.103448275862069</v>
+        <v>0.03896103896103896</v>
       </c>
     </row>
     <row r="6">
@@ -2906,31 +2906,31 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.0425531914893617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2954,49 +2954,49 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.06896551724137931</v>
       </c>
     </row>
     <row r="11">
@@ -3026,108 +3026,108 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.06451612903225806</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.007936507936507936</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -3146,19 +3146,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3170,19 +3170,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3194,19 +3194,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3218,19 +3218,19 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -3242,19 +3242,19 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Projeto</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03584229390681003</v>
+        <v>0.03823178016726404</v>
       </c>
     </row>
   </sheetData>
@@ -3388,322 +3388,322 @@
         <v>63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07936507936507936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.05</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.02597402597402598</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.01298701298701299</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03125</v>
+        <v>0.007936507936507936</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3781,19 +3781,19 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Projeto</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -3805,19 +3805,19 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -3936,132 +3936,132 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.04629629629629629</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.05357142857142857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="F5" s="5" t="n">
-        <v>0.05</v>
+        <v>0.04411764705882353</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -4080,36 +4080,36 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -4119,130 +4119,130 @@
         <v>28</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.009259259259259259</v>
       </c>
     </row>
     <row r="16">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0323943661971831</v>
+        <v>0.03943661971830986</v>
       </c>
     </row>
   </sheetData>
@@ -4499,49 +4499,49 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.07352941176470588</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04411764705882353</v>
+        <v>0.05357142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -4571,103 +4571,103 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.05</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.05</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -4676,27 +4676,27 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.009259259259259259</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -4715,36 +4715,36 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
@@ -4754,28 +4754,28 @@
         <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4787,19 +4787,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4811,19 +4811,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -4840,14 +4840,14 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4859,19 +4859,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.04225352112676056</v>
+        <v>0.03661971830985915</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2882,193 +2882,193 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.103448275862069</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.0425531914893617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.06451612903225806</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -3637,31 +3637,31 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.007936507936507936</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.007936507936507936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3709,19 +3709,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3733,19 +3733,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3757,19 +3757,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03106332138590203</v>
+        <v>0.02986857825567503</v>
       </c>
     </row>
   </sheetData>
@@ -3936,12 +3936,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -3960,12 +3960,12 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
@@ -3975,34 +3975,34 @@
         <v>56</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04411764705882353</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="6">
@@ -4032,25 +4032,25 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.05</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="8">
@@ -4080,12 +4080,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -4104,12 +4104,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -4128,97 +4128,97 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="15">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03943661971830986</v>
+        <v>0.04084507042253521</v>
       </c>
     </row>
   </sheetData>
@@ -4475,12 +4475,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -4490,103 +4490,103 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07352941176470588</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="F5" s="5" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.05882352941176471</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.07142857142857142</v>
@@ -4595,73 +4595,73 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.05</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="11">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03661971830985915</v>
+        <v>0.03943661971830986</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -573,10 +573,10 @@
         <v>80</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.075</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="4">
@@ -606,84 +606,84 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -693,58 +693,58 @@
         <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -755,14 +755,14 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -798,19 +798,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -822,19 +822,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -870,19 +870,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.03241491085899514</v>
+        <v>0.02917341977309562</v>
       </c>
     </row>
   </sheetData>
@@ -1121,187 +1121,187 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1385,19 +1385,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02431118314424635</v>
+        <v>0.02917341977309562</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -621,10 +621,10 @@
         <v>45</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -702,49 +702,49 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.01666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -755,14 +755,14 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -774,19 +774,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -798,19 +798,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -822,19 +822,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -846,19 +846,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -870,19 +870,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02917341977309562</v>
+        <v>0.02755267423014587</v>
       </c>
     </row>
   </sheetData>
@@ -1136,88 +1136,88 @@
         <v>45</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1229,61 +1229,61 @@
         <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.01666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1294,14 +1294,14 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1385,19 +1385,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3936,12 +3936,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -3960,12 +3960,12 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
@@ -3975,117 +3975,117 @@
         <v>56</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -4104,12 +4104,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.04084507042253521</v>
+        <v>0.03943661971830986</v>
       </c>
     </row>
   </sheetData>
@@ -4475,12 +4475,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -4499,12 +4499,12 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
@@ -4514,10 +4514,10 @@
         <v>56</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="5">
@@ -4547,46 +4547,46 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.07142857142857142</v>
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03943661971830986</v>
+        <v>0.03661971830985915</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -630,12 +630,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -645,21 +645,21 @@
         <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02755267423014587</v>
+        <v>0.02917341977309562</v>
       </c>
     </row>
   </sheetData>
@@ -1193,49 +1193,49 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03125</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02917341977309562</v>
+        <v>0.02755267423014587</v>
       </c>
     </row>
   </sheetData>
@@ -1603,10 +1603,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="4">
@@ -1708,12 +1708,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -1804,12 +1804,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.05351170568561873</v>
+        <v>0.05183946488294314</v>
       </c>
     </row>
   </sheetData>
@@ -2214,10 +2214,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="4">
@@ -2247,7 +2247,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2271,108 +2271,108 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -2391,115 +2391,115 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04180602006688963</v>
+        <v>0.0451505016722408</v>
       </c>
     </row>
   </sheetData>
@@ -2849,202 +2849,202 @@
         <v>62</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.08064516129032258</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.103448275862069</v>
+        <v>0.03896103896103896</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.103448275862069</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.06451612903225806</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02127659574468085</v>
       </c>
     </row>
     <row r="13">
@@ -3122,43 +3122,43 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3170,19 +3170,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3194,19 +3194,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3218,19 +3218,19 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Projeto</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -3242,19 +3242,19 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03823178016726404</v>
+        <v>0.03942652329749104</v>
       </c>
     </row>
   </sheetData>
@@ -3397,25 +3397,25 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="5">
@@ -3445,49 +3445,49 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="8">
@@ -3498,31 +3498,31 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -3541,73 +3541,73 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.01298701298701299</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.01298701298701299</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -4080,12 +4080,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -4104,49 +4104,49 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.025</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="12">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03943661971830986</v>
+        <v>0.0380281690140845</v>
       </c>
     </row>
   </sheetData>
@@ -4490,10 +4490,10 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="4">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03661971830985915</v>
+        <v>0.0380281690140845</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2882,97 +2882,97 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.103448275862069</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.03896103896103896</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="F9" s="5" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.103448275862069</v>
       </c>
     </row>
     <row r="10">
@@ -3002,139 +3002,139 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.02083333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.007936507936507936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3146,19 +3146,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3170,19 +3170,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3194,19 +3194,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03942652329749104</v>
+        <v>0.03823178016726404</v>
       </c>
     </row>
   </sheetData>
@@ -3421,49 +3421,49 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -3474,31 +3474,31 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -3517,145 +3517,145 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.01298701298701299</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.01298701298701299</v>
+        <v>0.02083333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.007936507936507936</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -3709,19 +3709,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3733,19 +3733,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3757,19 +3757,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.02986857825567503</v>
+        <v>0.02867383512544803</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2969,10 +2969,10 @@
         <v>29</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.103448275862069</v>
+        <v>0.06896551724137931</v>
       </c>
     </row>
     <row r="10">
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03823178016726404</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -3936,12 +3936,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -3951,21 +3951,21 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0380281690140845</v>
+        <v>0.03661971830985915</v>
       </c>
     </row>
   </sheetData>
@@ -4538,10 +4538,10 @@
         <v>68</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.04411764705882353</v>
       </c>
     </row>
     <row r="6">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0380281690140845</v>
+        <v>0.03661971830985915</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -4523,46 +4523,46 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04411764705882353</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>0.07142857142857142</v>
@@ -4571,25 +4571,25 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="8">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03661971830985915</v>
+        <v>0.0352112676056338</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -3936,12 +3936,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -3951,21 +3951,21 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0380281690140845</v>
+        <v>0.03661971830985915</v>
       </c>
     </row>
   </sheetData>
@@ -4523,46 +4523,46 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>0.07142857142857142</v>
@@ -4571,25 +4571,25 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="8">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0380281690140845</v>
+        <v>0.0352112676056338</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -582,73 +582,73 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.04210526315789474</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.09375</v>
+        <v>0.02105263157894737</v>
       </c>
     </row>
     <row r="7">
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02917341977309562</v>
+        <v>0.02593192868719611</v>
       </c>
     </row>
   </sheetData>
@@ -1073,73 +1073,73 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.04210526315789474</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.05</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02105263157894737</v>
       </c>
     </row>
     <row r="6">
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02755267423014587</v>
+        <v>0.02431118314424635</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -606,60 +606,60 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.09375</v>
+        <v>0.02105263157894737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.02105263157894737</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02593192868719611</v>
+        <v>0.02431118314424635</v>
       </c>
     </row>
   </sheetData>
@@ -1217,25 +1217,25 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.02222222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1289,19 +1289,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1385,19 +1385,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02431118314424635</v>
+        <v>0.0226904376012966</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -582,25 +582,25 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="5">
@@ -630,60 +630,60 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -693,34 +693,34 @@
         <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="10">
@@ -731,14 +731,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -774,19 +774,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -798,19 +798,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02431118314424635</v>
+        <v>0.02755267423014587</v>
       </c>
     </row>
   </sheetData>
@@ -1088,82 +1088,82 @@
         <v>80</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.05</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02105263157894737</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.02105263157894737</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
@@ -1217,25 +1217,25 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1289,19 +1289,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0226904376012966</v>
+        <v>0.02431118314424635</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -582,73 +582,73 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.09375</v>
+        <v>0.02105263157894737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.02105263157894737</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
@@ -702,49 +702,49 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -755,14 +755,14 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -774,19 +774,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -798,19 +798,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -822,19 +822,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -846,19 +846,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02593192868719611</v>
+        <v>0.02755267423014587</v>
       </c>
     </row>
   </sheetData>
@@ -1097,84 +1097,84 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.02105263157894737</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.02105263157894737</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -1184,58 +1184,58 @@
         <v>32</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1361,19 +1361,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1385,19 +1385,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02431118314424635</v>
+        <v>0.02106969205834684</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -573,10 +573,10 @@
         <v>80</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="4">
@@ -606,84 +606,84 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.02105263157894737</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.02105263157894737</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -693,58 +693,58 @@
         <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -755,14 +755,14 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -774,19 +774,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -798,19 +798,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -822,19 +822,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -846,19 +846,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1097,84 +1097,84 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.02105263157894737</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.02105263157894737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -1184,58 +1184,58 @@
         <v>32</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03125</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1289,19 +1289,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -582,36 +582,36 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.09375</v>
+        <v>0.04210526315789474</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -621,34 +621,34 @@
         <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.02105263157894737</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02755267423014587</v>
+        <v>0.03241491085899514</v>
       </c>
     </row>
   </sheetData>
@@ -1073,73 +1073,73 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.05</v>
+        <v>0.04210526315789474</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.02105263157894737</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02106969205834684</v>
+        <v>0.02431118314424635</v>
       </c>
     </row>
   </sheetData>
@@ -3960,49 +3960,49 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.05357142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03661971830985915</v>
+        <v>0.0352112676056338</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -558,49 +558,49 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="F3" s="5" t="n">
-        <v>0.075</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.04210526315789474</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5">
@@ -693,10 +693,10 @@
         <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="9">
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.03241491085899514</v>
+        <v>0.02917341977309562</v>
       </c>
     </row>
   </sheetData>
@@ -1088,10 +1088,10 @@
         <v>95</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.04210526315789474</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="4">
@@ -1121,12 +1121,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -1136,82 +1136,82 @@
         <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="9">
@@ -1289,19 +1289,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02431118314424635</v>
+        <v>0.02917341977309562</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -4080,169 +4080,169 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.025</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.009259259259259259</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.009259259259259259</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="16">
@@ -4401,10 +4401,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0352112676056338</v>
+        <v>0.03380281690140845</v>
       </c>
     </row>
   </sheetData>
@@ -4490,10 +4490,10 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="4">
@@ -4523,46 +4523,46 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>0.07142857142857142</v>
@@ -4571,97 +4571,97 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.05</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="11">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0352112676056338</v>
+        <v>0.03661971830985915</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -1651,58 +1651,58 @@
         <v>28</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.1153846153846154</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="8">
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.05183946488294314</v>
+        <v>0.04849498327759198</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2906,73 +2906,73 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="F7" s="5" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.03896103896103896</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.06896551724137931</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="10">
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.03464755077658303</v>
       </c>
     </row>
   </sheetData>
@@ -3421,60 +3421,60 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3493,12 +3493,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -3709,19 +3709,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3733,19 +3733,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3757,19 +3757,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3781,19 +3781,19 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -3805,19 +3805,19 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Projeto</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.02867383512544803</v>
+        <v>0.03106332138590203</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -1756,97 +1756,97 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="14">
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04849498327759198</v>
+        <v>0.04682274247491638</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2463,36 +2463,36 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Eletiva</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -2511,12 +2511,12 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Eletiva</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -2535,12 +2535,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Finanças</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -2559,19 +2559,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Finanças</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -2583,19 +2583,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0451505016722408</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
   </sheetData>
@@ -3565,115 +3565,115 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -3685,19 +3685,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03106332138590203</v>
+        <v>0.02986857825567503</v>
       </c>
     </row>
   </sheetData>
@@ -4475,12 +4475,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -4490,79 +4490,79 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>0.07142857142857142</v>
@@ -4571,97 +4571,97 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.05</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="11">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03661971830985915</v>
+        <v>0.03380281690140845</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -3960,60 +3960,60 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -4023,34 +4023,34 @@
         <v>28</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
@@ -4080,25 +4080,25 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.025</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="10">
@@ -4128,108 +4128,108 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02631578947368421</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.009259259259259259</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.009259259259259259</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -4239,28 +4239,28 @@
         <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4272,19 +4272,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -4296,19 +4296,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -4538,10 +4538,10 @@
         <v>56</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.05357142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -4595,121 +4595,121 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.05</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.009259259259259259</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.009259259259259259</v>
       </c>
     </row>
     <row r="13">
@@ -4835,19 +4835,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -4883,12 +4883,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03380281690140845</v>
+        <v>0.03098591549295775</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -678,49 +678,49 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="10">
@@ -731,14 +731,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -774,19 +774,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -798,19 +798,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -822,19 +822,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -846,19 +846,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.02917341977309562</v>
+        <v>0.03079416531604538</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -3960,49 +3960,49 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
@@ -4032,73 +4032,73 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.05</v>
+        <v>0.02941176470588235</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="10">
@@ -4475,49 +4475,49 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.131578947368421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="5">
@@ -4643,36 +4643,36 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -4691,49 +4691,49 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.009259259259259259</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>0.009259259259259259</v>
       </c>
     </row>
     <row r="14">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03098591549295775</v>
+        <v>0.03380281690140845</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2247,7 +2247,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -2295,49 +2295,49 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="9">
@@ -2348,31 +2348,31 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -2391,12 +2391,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -2415,25 +2415,25 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04180602006688963</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -1603,10 +1603,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="4">
@@ -1627,10 +1627,10 @@
         <v>54</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09259259259259259</v>
       </c>
     </row>
     <row r="5">
@@ -1684,60 +1684,60 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -1756,12 +1756,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -1771,10 +1771,10 @@
         <v>26</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03846153846153846</v>
       </c>
     </row>
     <row r="11">
@@ -1828,12 +1828,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1852,43 +1852,43 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1924,19 +1924,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Eletiva</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1948,12 +1948,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Eletiva</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -1972,12 +1972,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Finanças</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1996,12 +1996,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Finanças</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
@@ -2020,19 +2020,19 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -2214,10 +2214,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.08823529411764706</v>
+        <v>0.1029411764705882</v>
       </c>
     </row>
     <row r="4">
@@ -2391,73 +2391,73 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.025</v>
+        <v>0.03846153846153846</v>
       </c>
     </row>
     <row r="14">

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -645,10 +645,10 @@
         <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="7">
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.03079416531604538</v>
+        <v>0.03241491085899514</v>
       </c>
     </row>
   </sheetData>
@@ -1121,12 +1121,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -1136,58 +1136,58 @@
         <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.125</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
@@ -1217,25 +1217,25 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="10">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1289,19 +1289,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1385,19 +1385,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -3951,58 +3951,58 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07894736842105263</v>
       </c>
     </row>
     <row r="6">
@@ -4200,12 +4200,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
@@ -4215,28 +4215,28 @@
         <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4248,19 +4248,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4272,19 +4272,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -4296,19 +4296,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4320,19 +4320,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -4349,14 +4349,14 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -4475,49 +4475,49 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.131578947368421</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.131578947368421</v>
       </c>
     </row>
     <row r="5">
@@ -4595,97 +4595,97 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.05</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.025</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="12">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.03380281690140845</v>
+        <v>0.0352112676056338</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -3951,58 +3951,58 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="6">
@@ -4200,12 +4200,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
@@ -4215,28 +4215,28 @@
         <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4248,19 +4248,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4272,19 +4272,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -4296,19 +4296,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4320,19 +4320,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -4349,14 +4349,14 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -4475,49 +4475,49 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.131578947368421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.131578947368421</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="5">
@@ -4595,97 +4595,97 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.025</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.025</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="12">
@@ -4940,10 +4940,10 @@
         <v>710</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0352112676056338</v>
+        <v>0.03380281690140845</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2882,73 +2882,73 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="F6" s="8" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.03896103896103896</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -3002,91 +3002,91 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03125</v>
+        <v>0.03448275862068965</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -3098,19 +3098,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -3122,19 +3122,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3460,45 +3460,45 @@
         <v>48</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -3517,163 +3517,163 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.01298701298701299</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.01298701298701299</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -3685,19 +3685,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3709,19 +3709,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3733,19 +3733,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3757,19 +3757,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.02986857825567503</v>
+        <v>0.03106332138590203</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -1780,60 +1780,60 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1852,43 +1852,43 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1924,19 +1924,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Eletiva</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1948,12 +1948,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Eletiva</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -1972,12 +1972,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Finanças</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1996,7 +1996,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Finanças</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04682274247491638</v>
+        <v>0.0451505016722408</v>
       </c>
     </row>
   </sheetData>
@@ -2247,36 +2247,36 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1153846153846154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -2295,49 +2295,49 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="9">
@@ -2348,31 +2348,31 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04180602006688963</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -645,10 +645,10 @@
         <v>32</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="7">
@@ -999,10 +999,10 @@
         <v>617</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.03079416531604538</v>
+        <v>0.03241491085899514</v>
       </c>
     </row>
   </sheetData>
@@ -1121,12 +1121,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -1136,58 +1136,58 @@
         <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.125</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
@@ -1217,25 +1217,25 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="10">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Caro (Carolina Salles Kehl)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SMo (Samara Costa Moura)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1289,19 +1289,19 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1337,19 +1337,19 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1385,19 +1385,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1433,19 +1433,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -1780,60 +1780,60 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1852,43 +1852,43 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Apoio</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Apoio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SGa (Sabrina Gab)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -1924,19 +1924,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Eletiva</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1948,12 +1948,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Eletiva</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
@@ -1972,12 +1972,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Finanças</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1996,7 +1996,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Finanças</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04682274247491638</v>
+        <v>0.0451505016722408</v>
       </c>
     </row>
   </sheetData>
@@ -2247,36 +2247,36 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1153846153846154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -2295,49 +2295,49 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="9">
@@ -2348,31 +2348,31 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04180602006688963</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
   </sheetData>
@@ -2882,73 +2882,73 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="F6" s="8" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.03896103896103896</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -3002,91 +3002,91 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03125</v>
+        <v>0.03448275862068965</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -3098,19 +3098,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -3122,19 +3122,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3460,45 +3460,45 @@
         <v>48</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -3517,163 +3517,163 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.01298701298701299</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.01298701298701299</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -3685,19 +3685,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3709,19 +3709,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3733,19 +3733,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3757,19 +3757,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.02986857825567503</v>
+        <v>0.03106332138590203</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2930,49 +2930,49 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.06521739130434782</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="10">
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03464755077658303</v>
+        <v>0.03584229390681003</v>
       </c>
     </row>
   </sheetData>
@@ -3436,10 +3436,10 @@
         <v>32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.125</v>
+        <v>0.09375</v>
       </c>
     </row>
     <row r="6">
@@ -3517,84 +3517,84 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.01298701298701299</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.01298701298701299</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -3637,67 +3637,67 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3709,19 +3709,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3733,19 +3733,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03106332138590203</v>
+        <v>0.02986857825567503</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -1603,10 +1603,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="4">
@@ -2125,10 +2125,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0451505016722408</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
   </sheetData>
@@ -2214,10 +2214,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.08823529411764706</v>
       </c>
     </row>
     <row r="4">
@@ -2736,10 +2736,10 @@
         <v>598</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04180602006688963</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2810,49 +2810,49 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.07936507936507936</v>
+        <v>0.08064516129032258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.06349206349206349</v>
       </c>
     </row>
     <row r="5">
@@ -3002,73 +3002,73 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03448275862068965</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.03448275862068965</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="14">
@@ -3388,10 +3388,10 @@
         <v>63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.07936507936507936</v>
+        <v>0.06349206349206349</v>
       </c>
     </row>
     <row r="4">
@@ -3469,132 +3469,132 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.01298701298701299</v>
+        <v>0.02222222222222222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.01298701298701299</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
@@ -3613,25 +3613,25 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="14">

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -2906,12 +2906,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -2930,97 +2930,97 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.06521739130434782</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="F9" s="5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06451612903225806</v>
       </c>
     </row>
     <row r="12">
@@ -3299,10 +3299,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.03584229390681003</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
   </sheetData>
@@ -3613,91 +3613,91 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03125</v>
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3709,19 +3709,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -3733,19 +3733,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>837</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.02986857825567503</v>
+        <v>0.02867383512544803</v>
       </c>
     </row>
   </sheetData>

--- a/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
+++ b/Horario desenvolvido/Relatorio_Tempos_Cedidos_Proposta_3.xlsx
@@ -3951,10 +3951,10 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="4">
@@ -4176,36 +4176,36 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.009259259259259259</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
@@ -4215,28 +4215,28 @@
         <v>28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4248,19 +4248,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4272,19 +4272,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -4296,19 +4296,19 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -4320,19 +4320,19 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -4475,49 +4475,49 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.131578947368421</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.131578947368421</v>
       </c>
     </row>
     <row r="5">
@@ -4715,7 +4715,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -4724,34 +4724,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.009259259259259259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -4763,19 +4763,19 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -4787,19 +4787,19 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -4811,19 +4811,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
